--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0104.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0104.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đừng có nhìn ta với đôi mắt ỉu xìu như chó cưng thế. Dù ngươi có đi hỏi trực tiếp Chủ tịch, bà ấy cũng chẳng nói đâu.</t>
+          <t>Đừng có nhìn tao với đôi mắt ỉu xìu như chó cưng thế. Dù mày có đi hỏi trực tiếp Chủ tịch, bà ấy cũng chẳng nói đâu.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đợi ta một chút.</t>
+          <t>Đợi tao một chút.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Giờ ta tò mò quá... Nếu há miệng rộng hết cỡ, ngươi có thể nhét được bao nhiêu thứ vào đấy nhỉ?</t>
+          <t>Giờ ta tò mò quá... Nếu há miệng rộng hết cỡ, mày có thể nhét được bao nhiêu thứ vào đấy nhỉ?</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Thực ra ta hơi thất vọng về cậu...</t>
+          <t>Thực ra tao hơi thất vọng về cậu...</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ý cậu thật sự có giá trị với bọn ta. Cảm ơn vì đã trân trọng công sức của chúng tôi.</t>
+          <t>Ý cậu thật sự có giá trị với bọn tao. Cảm ơn vì đã trân trọng công sức của chúng tôi.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Mì Ly Kỳ Lạ Nửa Đêm, Bánh Mì "Nhai Thêm" Nhân Mì, và các hương vị Squeezy Jelly mới. Để ta lo!</t>
+          <t>Mì Ly Kỳ Lạ Nửa Đêm, Bánh Mì "Nhai Thêm" Nhân Mì, và các hương vị Squeezy Jelly mới. Để tao lo!</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Sau khi kiểm tra xong và giải quyết xong số vật liệu cùng tiền nong còn lại, Ta SẼ TỰ DO, EM ƠI, ÔI YÊÊÊÊÊ!</t>
+          <t>Sau khi kiểm tra xong và giải quyết xong số vật liệu cùng tiền nong còn lại, TAO SẼ TỰ DO, EM ƠI, ÔI YÊÊÊÊÊ!</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Bố cục này. Những đường mạch điện này. Chất lượng thi công... Trời ơi, ta làm tốt thật đấy. Giám sát giỏi nhất mà.</t>
+          <t>Bố cục này. Những đường mạch điện này. Chất lượng thi công... Trời ơi, tao làm tốt thật đấy. Giám sát giỏi nhất mà.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao rồi?</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Haha, ta sẽ không dành quá nhiều thời gian cho bản đánh giá đâu. Chỉ là tóm tắt vài bài học và phương pháp có thể dùng lại cho các dự án sau thôi.</t>
+          <t>Haha, tao sẽ không dành quá nhiều thời gian cho bản đánh giá đâu. Chỉ là tóm tắt vài bài học và phương pháp có thể dùng lại cho các dự án sau thôi.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ta lo cho cậu rồi, đừng lo... À, Balthasar, bí quyết sống thành công của ngươi là gì thế?</t>
+          <t>Tao lo cho cậu rồi, đừng lo... À, Balthasar, bí quyết sống thành công của mày là gì thế?</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Ta lo cho cậu rồi, đừng lo... À, Balthasar, bí quyết sống thành công của ngươi là gì thế?</t>
+          <t>Tao lo cho cậu rồi, đừng lo... À, Balthasar, bí quyết sống thành công của mày là gì thế?</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Haha, bệnh xá đá ta ra rồi đấy! Chỉ gãy vài cái xương với bỏng nhẹ thôi mà. Chuyện nhỏ!</t>
+          <t>Haha, bệnh xá đá tao ra rồi đấy! Chỉ gãy vài cái xương với bỏng nhẹ thôi mà. Chuyện nhỏ!</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Điều này hoàn toàn khác với những gì ta tưởng tượng. Những tòa nhà bị cuốn vào Bão Hư Không này thực ra lại đầy dấu vết hoạt động của động vật.</t>
+          <t>Điều này hoàn toàn khác với những gì tao tưởng tượng. Những tòa nhà bị cuốn vào Bão Hư Không này thực ra lại đầy dấu vết hoạt động của động vật.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Ha! Ngươi đang đánh giá thấp con Chuubill Gulpy quá đấy. Lần trước, cả cánh tay ta nó nuốt chửng luôn!</t>
+          <t>Ha! Mày đang đánh giá thấp con Chuubill Gulpy quá đấy. Lần trước, cả cánh tay tao nó nuốt chửng luôn!</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Vậy là Dark Thunderbolt cũng tham gia sự kiện này sao? Nhiều người bảo họ đã gặp {Male=anh ấy;Female=cô ấy} rồi đấy!!</t>
+          <t>Vậy là Dark Thunderbolt cũng tham gia sự kiện này sao? Nhiều người bảo họ đã gặp {Male=him;Female=her} rồi đấy!!</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Đúng thế! {Male=Anh ấy;Female=Chị ấy} còn cứu con khi con bị bọn Exoswarm hoang dã tấn công nữa cơ!</t>
+          <t>Đúng thế! {Male=He;Female=She} còn cứu con khi con bị bọn Exoswarm hoang dã tấn công nữa cơ!</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Này, {Male=anh ấy;Female=cô ấy} còn giúp ta tìm lại chiếc xe máy thám hiểm bị Soliskin cướp mất nữa cơ, hihi.</t>
+          <t>Này, {Male=he;Female=she} còn giúp tao tìm lại chiếc xe máy thám hiểm bị Soliskin cướp mất nữa cơ, hihi.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Sao lại công bằng được... Chỉ mình ta là người duy nhất trong cả Học viện chưa gặp được Dark Thunderbolt?!</t>
+          <t>Sao lại công bằng được... Chỉ mình tao là người duy nhất trong cả Học viện chưa gặp được Dark Thunderbolt?!</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Để ta nhắc lại: không được xả rác ở vùng hoang dã. Bỏ tất cả vào túi tái chế và mang về trạm cơ sở để xử lý.</t>
+          <t>Để tao nhắc lại: không được xả rác ở vùng hoang dã. Bỏ tất cả vào túi tái chế và mang về trạm cơ sở để xử lý.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Đua hả? Được thôi. Ta vừa tập luyện với Lynae đấy. Học được kha khá chiêu mới. Ta có thể đánh bại ngươi mà chỉ cần một tay thôi.</t>
+          <t>Đua hả? Được thôi. Tao vừa tập luyện với Lynae đấy. Học được kha khá chiêu mới. Tao có thể đánh bại mày mà chỉ cần một tay thôi.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Ta chưa từng dạy ngươi điều gì cả...</t>
+          <t>Tao chưa từng dạy mày điều gì cả...</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tch. Ai bảo ta có thư nhập học của Viện trong tay mà còn đòi nhường cơ hội cho đàn em chứ?</t>
+          <t>Tch. Ai bảo tao có thư nhập học của Viện trong tay mà còn đòi nhường cơ hội cho đàn em chứ?</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Ha. Bắt chước hả. Dù ngươi có lén theo thì ta vẫn sẽ đăng bài trước.</t>
+          <t>Ha. Bắt chước hả. Dù mày có lén theo thì tao vẫn sẽ đăng bài trước.</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Haha, ai thèm quan tâm chứ? Đồ nói dối. Đồ tự cao. Ta sẽ lấy dữ liệu lõi trước cậu. Đợi mà xem.</t>
+          <t>Haha, ai thèm quan tâm chứ? Đồ nói dối. Đồ tự cao. Tao sẽ lấy dữ liệu lõi trước cậu. Đợi mà xem.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Cậu cắt cả một khúc to như thế! Mẹ cây có chịu nổi không?</t>
+          <t>bạn cắt cả một khúc to như thế! Mẹ cây có chịu nổi không?</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Cậu cắt cả một khúc to như thế! Mẹ cây có chịu nổi không?</t>
+          <t>bạn cắt cả một khúc to như thế! Mẹ cây có chịu nổi không?</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Ta nghe nói ngươi gửi yêu cầu phát triển gel năng lượng vị ẩm thực Royan à?</t>
+          <t>Tao nghe nói mày gửi yêu cầu phát triển gel năng lượng vị ẩm thực Royan à?</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ta còn hơn chục dự án Solvein Heartwood đang chờ trên bàn. Thật sự không có thời gian đâu.</t>
+          <t>Tao còn hơn chục dự án Solvein Heartwood đang chờ trên bàn. Thật sự không có thời gian đâu.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chào cậu, chúc chuyến thám hiểm an toàn.</t>
+          <t>Chào bạn, chúc chuyến thám hiểm an toàn.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Cảm ơn người tiên phong biên giới, những đóng góp quý báu của cậu đã giúp ích rất nhiều cho chuyến thám hiểm này.</t>
+          <t>Cảm ơn người tiên phong biên giới, những đóng góp quý báu của bạn đã giúp ích rất nhiều cho chuyến thám hiểm này.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Không phải ta. Chuyện đó chưa từng xảy ra. Ta thề bằng cả số tín dụng của mình.</t>
+          <t>Không phải tao. Chuyện đó chưa từng xảy ra. Tao thề bằng cả số tín dụng của mình.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Trần nhà đó... trông quen quá. Ta quay lại Học viện rồi à?</t>
+          <t>Trần nhà đó... trông quen quá. Tao quay lại Học viện rồi à?</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Mỗi lần nghĩ đến những đồng đội đã ngã xuống chỉ để cứu hai thằng ngốc phá luật, ta lại sôi máu.</t>
+          <t>Mỗi lần nghĩ đến những đồng đội đã ngã xuống chỉ để cứu hai thằng ngốc phá luật, tao lại sôi máu.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Trả lời ta đi, Hiroyuki! Ngươi là ai? Ngươi đang làm gì ở đây? Tại sao lại đến chỗ này?</t>
+          <t>Trả lời tao đi, Hiroyuki! Mày là ai? Mày đang làm gì ở đây? Tại sao lại đến chỗ này?</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Khắc sâu vào đầu bọn ngươi! Các ngươi là ĐỒNG ĐIỆU VIÊN của Học viện Rabelle, Học viện Startorch!</t>
+          <t>Khắc sâu vào đầu bọn mày! Các ngươi là ĐỒNG ĐIỆU VIÊN của Học viện Rabelle, Học viện Startorch!</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Trả lời ta đi, Hiroyuki. Ngươi đã bao giờ thắc mắc tại sao cả Exostrider lẫn Mechascouts đều có hình dạng con người chưa?</t>
+          <t>Trả lời tao đi, Hiroyuki. Mày đã bao giờ thắc mắc tại sao cả Exostrider lẫn Mechascouts đều có hình dạng con người chưa?</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Sai! Với khả năng của một Đồng Bộ Giả, ngươi nghĩ mình không thể điều khiển một con robot bốn chân à? Hay một khẩu đại pháo khủng bố?</t>
+          <t>Sai! Với khả năng của một Đồng Bộ Giả, mày nghĩ mình không thể điều khiển một con robot bốn chân à? Hay một khẩu đại pháo khủng bố?</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Ừ. Tiếc là ta không có mặt ở đó. Chắc hẳn cảnh tượng đó phải hùng vĩ lắm.</t>
+          <t>Ừ. Tiếc là tao không có mặt ở đó. Chắc hẳn cảnh tượng đó phải hùng vĩ lắm.</t>
         </is>
       </c>
     </row>
